--- a/docentes/Camarillo Aburto Raymundo - Estadisticos 20211.xlsx
+++ b/docentes/Camarillo Aburto Raymundo - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -55,9 +55,6 @@
     <t>3BLCM</t>
   </si>
   <si>
-    <t>3APV</t>
-  </si>
-  <si>
     <t>3ARHV</t>
   </si>
   <si>
@@ -82,79 +79,70 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CARRERA</t>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CANTELLAN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>LUNA</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>ZAVALETA</t>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>CONCHE</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>ALFREDO</t>
+    <t>CONSTANZA XIMENA</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
   </si>
   <si>
     <t>JESUS ANTONIO</t>
   </si>
   <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>ALEXA</t>
+  </si>
+  <si>
     <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>YAMILE</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>GERMAN ERNESTO</t>
-  </si>
-  <si>
-    <t>MARIA MAGDALENA</t>
   </si>
   <si>
     <t>SAMANTHA</t>
@@ -515,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -633,22 +621,22 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>57.14</v>
+        <v>80</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -659,47 +647,21 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>80</v>
+        <v>57.14</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>21</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>9</v>
-      </c>
-      <c r="F7">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>57.14</v>
-      </c>
-      <c r="H7">
         <v>6.2</v>
       </c>
     </row>
@@ -710,7 +672,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -753,16 +715,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="H2">
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -776,16 +741,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+      <c r="H3">
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -799,16 +767,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>68.56999999999999</v>
+      </c>
+      <c r="H4">
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -819,19 +790,22 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>91.43000000000001</v>
+      </c>
+      <c r="H5">
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -842,41 +816,18 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>21</v>
-      </c>
-      <c r="D7">
-        <v>21</v>
-      </c>
-      <c r="E7">
-        <v>21</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
         <v>0</v>
       </c>
     </row>
@@ -887,7 +838,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -933,16 +884,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -959,16 +910,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>68.75</v>
+        <v>87.5</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -985,16 +936,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>48.57</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1005,22 +956,22 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>57.14</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1031,47 +982,21 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>80</v>
+        <v>57.14</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>21</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>9</v>
-      </c>
-      <c r="F7">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>57.14</v>
-      </c>
-      <c r="H7">
         <v>6.2</v>
       </c>
     </row>
@@ -1082,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1091,154 +1016,154 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920263</v>
+        <v>20330051920151</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920326</v>
+        <v>20330051920320</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920396</v>
+        <v>20330051920325</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920040</v>
+        <v>20330051920326</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920295</v>
+        <v>20330051920039</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920311</v>
+        <v>20330051920296</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1247,21 +1172,21 @@
         <v>11</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920134</v>
+        <v>20330051920396</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1270,21 +1195,21 @@
         <v>13</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920299</v>
+        <v>20330051920309</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1293,30 +1218,7 @@
         <v>11</v>
       </c>
       <c r="G9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920309</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Camarillo Aburto Raymundo - Estadisticos 20211.xlsx
+++ b/docentes/Camarillo Aburto Raymundo - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="45">
   <si>
     <t>Mat</t>
   </si>
@@ -94,6 +94,9 @@
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
@@ -115,12 +118,12 @@
     <t>CONCHE</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>PRADO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
@@ -137,6 +140,9 @@
   </si>
   <si>
     <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
   </si>
   <si>
     <t>ALEXA</t>
@@ -1007,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1045,10 +1051,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1057,7 +1063,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1068,10 +1074,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1091,10 +1097,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1114,10 +1120,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1137,10 +1143,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1154,16 +1160,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920296</v>
+        <v>20330051920287</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1172,53 +1178,76 @@
         <v>11</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920396</v>
+        <v>20330051920296</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920309</v>
+        <v>20330051920396</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920309</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
         <v>11</v>
       </c>
-      <c r="G9">
-        <v>2</v>
+      <c r="G10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Camarillo Aburto Raymundo - Estadisticos 20211.xlsx
+++ b/docentes/Camarillo Aburto Raymundo - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -82,9 +82,6 @@
     <t>TORRES</t>
   </si>
   <si>
-    <t>CANTELLAN</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -97,18 +94,12 @@
     <t>CABRERA</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>LARA</t>
-  </si>
-  <si>
     <t>CARRILLO</t>
   </si>
   <si>
@@ -130,9 +121,6 @@
     <t>CONSTANZA XIMENA</t>
   </si>
   <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
     <t>ANGEL DAVID</t>
   </si>
   <si>
@@ -146,9 +134,6 @@
   </si>
   <si>
     <t>ALEXA</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
   </si>
   <si>
     <t>SAMANTHA</t>
@@ -825,16 +810,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>66.67</v>
+      </c>
+      <c r="H6">
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -994,16 +982,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="H6">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -1013,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1051,10 +1039,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1063,21 +1051,21 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920320</v>
+        <v>20330051920325</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1086,21 +1074,21 @@
         <v>13</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920325</v>
+        <v>20330051920326</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1109,27 +1097,27 @@
         <v>13</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920326</v>
+        <v>20330051920039</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1137,22 +1125,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920039</v>
+        <v>20330051920287</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1160,16 +1148,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920287</v>
+        <v>20330051920296</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1183,16 +1171,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920296</v>
+        <v>20330051920309</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1201,52 +1189,6 @@
         <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920396</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920309</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Camarillo Aburto Raymundo - Estadisticos 20211.xlsx
+++ b/docentes/Camarillo Aburto Raymundo - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -79,61 +79,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
+    <t>MARCIAL</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>PRADO</t>
+    <t>RAMON</t>
   </si>
   <si>
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>CONSTANZA XIMENA</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>ALEXA</t>
+    <t>IVAN DE JESUS</t>
+  </si>
+  <si>
+    <t>MEILYN ADABEL</t>
   </si>
   <si>
     <t>SAMANTHA</t>
@@ -878,16 +845,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -904,16 +871,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -930,13 +897,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>68.56999999999999</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H4">
         <v>7.5</v>
@@ -956,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>91.43000000000001</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -982,16 +949,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1001,7 +968,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1033,16 +1000,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920151</v>
+        <v>20330051920136</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
         <v>26</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1051,144 +1018,52 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920325</v>
+        <v>20330051920148</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920326</v>
+        <v>20330051920309</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920039</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920287</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920296</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920309</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
         <v>1</v>
       </c>
     </row>
